--- a/profiles/yes/organizations.xlsx
+++ b/profiles/yes/organizations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,12 +439,17 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>website</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>status</t>
         </is>
       </c>
     </row>
@@ -469,12 +474,17 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://mastercardfdn.org/</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -497,12 +507,17 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.alikodangotefoundation.org/</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -525,12 +540,17 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://www.tonyelumelufoundation.org/</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -553,12 +573,17 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://jacobsfoundation.org/</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -581,12 +606,17 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.rockefellerfoundation.org/</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -609,12 +639,17 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://echidnagiving.org/</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -637,12 +672,17 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://sawirisfoundation.org/</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -665,12 +705,17 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://hewlett.org/</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -693,12 +738,17 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.worldbank.org/</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -721,12 +771,17 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.afdb.org/en</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -749,12 +804,17 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.giz.de/en</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -777,12 +837,17 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.gov.uk/government/organisations/foreign-commonwealth-development-office</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -805,12 +870,17 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.afd.fr/en</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -833,12 +903,17 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://international-partnerships.ec.europa.eu/</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -861,12 +936,17 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.ilo.org/</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,12 +969,17 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.generationunlimited.org/</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -917,12 +1002,17 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://kosmosinnovationcenter.com/</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -945,12 +1035,17 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://www.dangote.com/</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -973,12 +1068,17 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://www.mtn.com/</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1001,12 +1101,17 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://equitygroupfoundation.com/</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1029,12 +1134,17 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://www.standardbank.com/</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1057,12 +1167,17 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://youthconnektafrica.org/</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1085,12 +1200,17 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.schoolforlifegh.org/</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1113,12 +1233,17 @@
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://leapafrica.org/</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1141,12 +1266,17 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.harambee.co.za/</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1169,12 +1299,17 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://www.experienceeducate.org/</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1197,12 +1332,17 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>https://camfed.org/</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1225,12 +1365,17 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://waawfoundation.org/</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1253,12 +1398,17 @@
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>https://www.akazikanoze.org/</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1281,12 +1431,17 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>https://youthbusiness.org/</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1309,12 +1464,17 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>https://ctvet.gov.gh/</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1337,12 +1497,17 @@
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://www.rtb.gov.rw/</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1365,12 +1530,17 @@
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>https://agenceemploijeunes.ci/</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1393,12 +1563,17 @@
           <t>Niger</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>https://www.anpe-niger.ne/</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1421,12 +1596,17 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://www.sayouth.org.za/</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1449,12 +1629,17 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://prosperidadsocial.gov.co/</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1477,12 +1662,17 @@
           <t>Bangladesh</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>https://www.brac.net/</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1505,12 +1695,17 @@
           <t>India</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.pratham.org/</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1533,12 +1728,17 @@
           <t>Mexico</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>https://jovenesconstruyendoelfuturo.stps.gob.mx/</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1561,12 +1761,683 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>https://www.generation.org/</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>O041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>International Initiative for Impact Evaluation (3ie)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Evidence platform</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Evidence gap maps and systematic reviews say where the evidence runs out.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.3ieimpact.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>O042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Abdul Latif Jameel Poverty Action Lab (J-PAL)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Research institute</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Runs and catalogues trials, and publishes what remains untested.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.povertyactionlab.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>O043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Innovations for Poverty Action (IPA)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Research institute</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Trials on youth employment, with research agendas of its own.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://poverty-action.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>O044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Campbell Collaboration</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Evidence platform</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Systematic reviews that state what the evidence cannot yet settle.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.campbellcollaboration.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>O045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>African Economic Research Consortium (AERC)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>African research institute</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sets research agendas for African economies and trains the researchers.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://aercafrica.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>O046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>African Population and Health Research Center (APHRC)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>African research institute</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>African-led research on youth, education, and work, with its own agendas.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://aphrc.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>O047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Association for the Development of Education in Africa (ADEA)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>African policy network</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ministers' network on education and skills systems across the continent.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.adeanet.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>O048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>UNESCO-UNEVOC International Centre for TVET</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>The reference body on training systems, and on what is unknown about them.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://unevoc.unesco.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>O049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>International Development Research Centre (IDRC)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Research funder</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Funds African research and publishes where it sees the thin areas.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://idrc-crdi.ca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>O050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Research on Improving Systems of Education (RISE)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Research programme</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>System-level education research, the shape of question ACET asks.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://riseprogramme.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>O051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>INCLUDE Knowledge Platform</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Knowledge platform</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>African and Dutch research on inclusive development and youth employment.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://includeplatform.net/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>O052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>IZA Institute of Labor Economics</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Research institute</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Labour-market evidence, including growth and labour markets in low-income countries.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.iza.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>O053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ODI Global</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Research institute</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Policy research on jobs, informality, and the future of work.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://odi.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>O054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Institute of Development Studies (IDS)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Research institute</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Research on work, informality, and youth transitions.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.ids.ac.uk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>O055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Young Lives, University of Oxford</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Research programme</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Long-run study of young people's transitions from school to work.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.younglives.org.uk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>O056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>African Union Development Agency (AUDA-NEPAD)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>African policy body</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Continental skills and employment strategy, and the gaps it names.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.nepad.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>O057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>United Nations Economic Commission for Africa (UNECA)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Economic transformation research, the frame ACET works in.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.uneca.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>O058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Partnership for Economic Policy (PEP)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Research funder</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Funds and publishes southern-led labour-market research.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.pep-net.org/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
